--- a/input_data/sna_country_data/MEX/CSI_18.xlsx
+++ b/input_data/sna_country_data/MEX/CSI_18.xlsx
@@ -5,8 +5,8 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Tabulado" sheetId="1" r:id="Rfce18004d54a498e"/>
-    <sheet name="MetaInfo" sheetId="2" r:id="R689f43142b624f99"/>
+    <sheet name="Tabulado" sheetId="1" r:id="Rb9b95c117290465e"/>
+    <sheet name="MetaInfo" sheetId="2" r:id="R89d87f6650534fcb"/>
   </sheets>
 </workbook>
 </file>
@@ -39,7 +39,7 @@
     <t>Instituto Nacional de Estadística y Geografía (INEGI).</t>
   </si>
   <si>
-    <t>Sistema de Cuentas Nacionales de México. Cuentas por Sectores Institucionales. Año Base 2018. Serie 2003-2022. 2022 revisada</t>
+    <t>Sistema de Cuentas Nacionales de México. Cuentas por Sectores Institucionales. Año Base 2018. Serie 2003-2024. 2024 Revisada</t>
   </si>
   <si>
     <t>Cuentas institucionales de la economía, por sector/ Precios corrientes en millones de pesos/ 2018</t>
@@ -1189,19 +1189,19 @@
     <t>COBERTURA TEMPORAL</t>
   </si>
   <si>
-    <t>2003-01-2022-12</t>
+    <t>2003-01-2024-12</t>
   </si>
   <si>
     <t>DESCRIPCIÓN PERIODO</t>
   </si>
   <si>
-    <t>Serie 2003 a 2022. 2022 Revisada</t>
+    <t>Serie 2003 a 2024. 2024 Revisada</t>
   </si>
   <si>
     <t>FECHA DE ACTUALIZACIÓN</t>
   </si>
   <si>
-    <t>2024-06-28</t>
+    <t>2026-06-30</t>
   </si>
 </sst>
 </file>
@@ -26177,7 +26177,7 @@
     <mergeCell ref="A5:A8"/>
   </mergeCells>
   <headerFooter/>
-  <legacyDrawing r:id="R76959f1582ae414d"/>
+  <legacyDrawing r:id="R17d1383d39c24676"/>
 </worksheet>
 </file>
 
